--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260907.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260907.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -601,44 +601,44 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>922,437,000</t>
+          <t>179,341,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.77%</t>
+          <t>9.59%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>179,341,000</t>
+          <t>922,437,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.58%</t>
+          <t>9.56%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.75%</t>
+          <t>6.67%</t>
         </is>
       </c>
     </row>
@@ -682,73 +682,73 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.26%</t>
+          <t>6.06%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>109,122,000</t>
+          <t>190,401,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.94%</t>
+          <t>4.19%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>604,027,270</t>
+          <t>109,122,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.88%</t>
+          <t>3.91%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>190,401,000</t>
+          <t>604,027,270</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.83%</t>
+          <t>3.82%</t>
         </is>
       </c>
     </row>
@@ -770,95 +770,95 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.52%</t>
+          <t>3.76%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>132,826,945</t>
+          <t>27,829,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>3.12%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>64,742,000</t>
+          <t>449,396,250</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>3.07%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>27,829,000</t>
+          <t>132,826,945</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>3.05%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>449,396,250</t>
+          <t>64,742,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>2.98%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>2.75%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.72%</t>
+          <t>2.73%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>2.70%</t>
         </is>
       </c>
     </row>
@@ -946,161 +946,161 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.56%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>233,108,056</t>
+          <t>26,729,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.55%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>26,729,000</t>
+          <t>233,108,056</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.52%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>131,081,000</t>
+          <t>99,718,442</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>2.39%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>145,204,000</t>
+          <t>131,081,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.36%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>99,718,442</t>
+          <t>145,204,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>196,411,000</t>
+          <t>29,496,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.27%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>29,496,000</t>
+          <t>196,411,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.27%</t>
         </is>
       </c>
     </row>
@@ -1122,24 +1122,24 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.10%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>191,053,000</t>
+          <t>35,705,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,22 +1151,22 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>35,705,000</t>
+          <t>191,053,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>1.94%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.84%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.77%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.76%</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>B618CW</t>
+          <t>B95553</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>P11台積1B</t>
+          <t>P08凱控1B</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>200,000,000</t>
+          <t>100,000,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1297,17 +1297,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>B95553</t>
+          <t>B96525</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>P08凱控1B</t>
+          <t>P11元金2</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>120,000,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1315,17 +1315,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>B95555</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>P09凱控1B</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>185,000,000</t>
+          <t>31,393,710,787</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
@@ -1333,17 +1333,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>B96525</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>P11元金2</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>120,000,000</t>
+          <t>5,675,637,750</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr"/>
@@ -1351,74 +1351,20 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>B97872</t>
+          <t>PFUR_NTD</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>P13富邦金1</t>
+          <t>PAYABLES FOR UNITS REDEEMED</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>45,000,000</t>
+          <t>-1,436,931,750</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>C_NTD</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>CASH</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>31,502,675,226</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>M_NTD</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>MARGIN</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>5,391,455,550</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>PFUR_NTD</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>PAYABLES FOR UNITS REDEEMED</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>-1,132,986,009</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
